--- a/output/pdf_financials_xlsx/TCL.A.xlsx
+++ b/output/pdf_financials_xlsx/TCL.A.xlsx
@@ -3170,55 +3170,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>20.1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>76</v>
+        <v>19.1</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>121.8</v>
+        <v>18.1</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>52.4</v>
+        <v>14.1</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>14.7</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>70</v>
+        <v>16.2</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>38.4</v>
+        <v>15.9</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>282.7</v>
+        <v>18.4</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>24.7</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>243.9</v>
+        <v>20</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>274.7</v>
+        <v>20.3</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>272.4</v>
+        <v>24.4</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>79.7</v>
+        <v>21.8</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>194.6</v>
+        <v>20.6</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>344.5</v>
+        <v>21.7</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>91.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">

--- a/output/pdf_financials_xlsx/TCL.A.xlsx
+++ b/output/pdf_financials_xlsx/TCL.A.xlsx
@@ -2361,52 +2361,52 @@
         <v>34.7</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>36.3</v>
+        <v>31.9</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>35.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>38.6</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>247.1</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>213.7</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>231.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>45.7</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>185.2</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35">
@@ -2477,52 +2477,52 @@
         <v>34.7</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>36.3</v>
+        <v>31.9</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>35.2</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>38.6</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>247.1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>213.7</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>231.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>45.7</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>185.2</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37">
@@ -3170,55 +3170,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>20.1</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>19.1</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>18.1</v>
+        <v>46.8</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>14.7</v>
+        <v>53.6</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>14.1</v>
+        <v>26</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>14.7</v>
+        <v>29.9</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>16.2</v>
+        <v>31.4</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>15.9</v>
+        <v>21.7</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>18.4</v>
+        <v>35.6</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>24.7</v>
+        <v>31.6</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>20</v>
+        <v>30.2</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>20.3</v>
+        <v>33.7</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>24.4</v>
+        <v>41.3</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>21.8</v>
+        <v>34</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>20.6</v>
+        <v>57.6</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>21.7</v>
+        <v>159.3</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>25</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="49">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">

--- a/output/pdf_financials_xlsx/TCL.A.xlsx
+++ b/output/pdf_financials_xlsx/TCL.A.xlsx
@@ -7861,7 +7861,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="G126" s="3" t="n">
         <v>0</v>
@@ -39742,7 +39742,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TCL.A.xlsx
+++ b/output/pdf_financials_xlsx/TCL.A.xlsx
@@ -1573,7 +1573,7 @@
         <v>-168.5</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-16.2</v>
+        <v>-7.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>111</v>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-17.7</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>27.4</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>-7.4</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
@@ -2709,52 +2709,52 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>32.7</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>27.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>37.1</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>39.5</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>49.8</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>54.6</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>48.1</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>58.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>66.8</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>55.4</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="41">
@@ -2767,52 +2767,52 @@
         <v>306</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>428.8</v>
+        <v>461.5</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>425.5</v>
+        <v>450.3</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>449.8</v>
+        <v>475.3</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>419.2</v>
+        <v>447.1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>415.1</v>
+        <v>447.1</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>393</v>
+        <v>430.1</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>401.9</v>
+        <v>441.4</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>380.6</v>
+        <v>430.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>565.4</v>
+        <v>620</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>520.7</v>
+        <v>568.8</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>461.2</v>
+        <v>526.1</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>496.1</v>
+        <v>554.7</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>575.7</v>
+        <v>654.8</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>514.7</v>
+        <v>581.5</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>504.4</v>
+        <v>559.8</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>468.1</v>
+        <v>517</v>
       </c>
     </row>
     <row r="42">
@@ -3173,52 +3173,52 @@
         <v>67.59999999999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>47.7</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>46.8</v>
+        <v>22</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>53.6</v>
+        <v>28.1</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>29.9</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>31.4</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>35.6</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>31.6</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>30.2</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>33.7</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>41.3</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>57.6</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>159.3</v>
+        <v>103.9</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>44.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6281,13 +6281,13 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-64.09999999999999</v>
+        <v>-81.8</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>146</v>
+        <v>173.4</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>99.8</v>
+        <v>128.4</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-175.9</v>
@@ -7604,10 +7604,10 @@
         <v>0</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-32.3</v>
       </c>
       <c r="R121" s="3" t="n">
-        <v>0</v>
+        <v>-16.3</v>
       </c>
     </row>
     <row r="122">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>0</v>
+        <v>281.4</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
@@ -7690,7 +7690,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H123" s="3" t="n">
         <v>0</v>
@@ -7711,10 +7711,10 @@
         <v>0</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>0</v>
+        <v>399.3</v>
       </c>
       <c r="O123" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P123" s="3" t="n">
         <v>0</v>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>281.4</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -7806,7 +7806,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H125" s="3" t="n">
         <v>0</v>
@@ -7827,10 +7827,10 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>399.3</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P125" s="3" t="n">
         <v>0</v>
@@ -10461,7 +10461,11 @@
           <t>Lease liabilities 24</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -19234,7 +19238,11 @@
           <t>Lease liabilities 14</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -28591,7 +28599,11 @@
           <t>Shares repurchased 21</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -30904,7 +30916,11 @@
           <t>Increase in long-term debt 24</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -31876,7 +31892,11 @@
           <t>Increase in long-term debt 25</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -38138,7 +38158,11 @@
           <t>Increase in long-term debt 19</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -40449,7 +40473,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -42144,7 +42172,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E351" s="5" t="n">
         <v>-81.8</v>
       </c>
@@ -42338,11 +42370,7 @@
           <t>Net income (loss) from continuing operations</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D353" t="inlineStr"/>
       <c r="E353" s="5" t="n">
         <v>-64.09999999999999</v>
       </c>
@@ -45128,7 +45156,11 @@
           <t>Future income taxes 6</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E381" s="5" t="n">
         <v>-22.6</v>
       </c>
@@ -46423,7 +46455,11 @@
           <t>Increase in long-term debt 15</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E394" s="5" t="n">
         <v>281.4</v>
       </c>
@@ -70426,7 +70462,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D641" t="inlineStr"/>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E641" t="inlineStr">
         <is>
           <t>-</t>
@@ -70521,7 +70561,11 @@
           <t>Net loss from discontinued operations 10</t>
         </is>
       </c>
-      <c r="D642" t="inlineStr"/>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E642" t="inlineStr">
         <is>
           <t>-</t>
@@ -72422,7 +72466,7 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
@@ -74830,7 +74874,7 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E685" s="5" t="n">
